--- a/resultados/xambre/inventario_externos.xlsx
+++ b/resultados/xambre/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1938"/>
+  <dimension ref="A1:G2182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66412,6 +66412,8302 @@
         </is>
       </c>
     </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F145%2Fdispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="F1939" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1939" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F145%2Fdispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="F1940" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1940" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F145%2Fdispensa-de-licitacao-n-0102023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2023</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="F1941" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1941" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F145%2Fdispensa-de-licitacao-n-0102023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2023</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr"/>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="F1942" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1942" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F143%2Fdispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="F1943" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1943" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F143%2Fdispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="F1944" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1944" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F143%2Fdispensa-de-licitacao-n-0062023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2023</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="F1945" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1945" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F143%2Fdispensa-de-licitacao-n-0062023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2023</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr"/>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="F1946" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1946" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F144%2Fdispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="F1947" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1947" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F144%2Fdispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="F1948" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1948" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F144%2Fdispensa-de-licitacao-n-0082023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2023</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="F1949" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1949" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F144%2Fdispensa-de-licitacao-n-0082023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2023</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr"/>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="F1950" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1950" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F142%2Fdispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="F1951" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1951" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F142%2Fdispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="F1952" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1952" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F142%2Fdispensa-de-licitacao-n-0072023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2023</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="F1953" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1953" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F142%2Fdispensa-de-licitacao-n-0072023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2023</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr"/>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="F1954" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1954" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F141%2Fdispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="F1955" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1955" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F141%2Fdispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="F1956" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1956" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F141%2Fdispensa-de-licitacao-n-0032023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2023</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="F1957" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1957" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F141%2Fdispensa-de-licitacao-n-0032023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2023</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr"/>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="F1958" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1958" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F140%2Fdispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="F1959" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1959" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F140%2Fdispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="F1960" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1960" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F140%2Fdispensa-de-licitacao-n-0042023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2023</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="F1961" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1961" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F140%2Fdispensa-de-licitacao-n-0042023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2023</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr"/>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="F1962" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1962" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F139%2Fdispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="F1963" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1963" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F139%2Fdispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="F1964" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1964" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F139%2Fdispensa-de-licitacao-n-0022023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2023</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="F1965" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1965" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F139%2Fdispensa-de-licitacao-n-0022023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2023</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr"/>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="F1966" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1966" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+014%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F137%2Fdispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="F1967" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1967" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F137%2Fdispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="F1968" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1968" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F137%2Fdispensa-de-licitacao-n-0142022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+014%2F2022</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="F1969" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1969" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F137%2Fdispensa-de-licitacao-n-0142022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+014%2F2022</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr"/>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="F1970" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1970" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+013%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F136%2Fdispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="F1971" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1971" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F136%2Fdispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="F1972" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1972" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F136%2Fdispensa-de-licitacao-n-0132022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+013%2F2022</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="F1973" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1973" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F136%2Fdispensa-de-licitacao-n-0132022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+013%2F2022</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr"/>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="F1974" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1974" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2023 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F138%2Fdispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="F1975" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1975" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F138%2Fdispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="F1976" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1976" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F138%2Fdispensa-de-licitacao-n-0012023&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2023</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="F1977" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1977" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F138%2Fdispensa-de-licitacao-n-0012023&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2023</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr"/>
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="F1978" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1978" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F135%2Fdispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="F1979" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1979" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F135%2Fdispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="F1980" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1980" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F135%2Fdispensa-de-licitacao-n-0122022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2022</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="F1981" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1981" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F135%2Fdispensa-de-licitacao-n-0122022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2022</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr"/>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="F1982" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1982" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F133%2Fdispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="F1983" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1983" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F133%2Fdispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="F1984" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1984" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F133%2Fdispensa-de-licitacao-n-0102022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2022</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="F1985" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1985" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F133%2Fdispensa-de-licitacao-n-0102022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2022</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr"/>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="F1986" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1986" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F134%2Fdispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="F1987" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1987" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F134%2Fdispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="F1988" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1988" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F134%2Fdispensa-de-licitacao-n-0112022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2022</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="F1989" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1989" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F134%2Fdispensa-de-licitacao-n-0112022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2022</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr"/>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="F1990" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1990" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F132%2Fdispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="F1991" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1991" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F132%2Fdispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="F1992" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1992" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F132%2Fdispensa-de-licitacao-n-0092022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2022</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="F1993" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1993" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F132%2Fdispensa-de-licitacao-n-0092022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2022</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr"/>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="F1994" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1994" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F131%2Fdispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="F1995" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1995" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F131%2Fdispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="F1996" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1996" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F131%2Fdispensa-de-licitacao-n-0082022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2022</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="F1997" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1997" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F131%2Fdispensa-de-licitacao-n-0082022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2022</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr"/>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="F1998" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1998" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F130%2Fdispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="F1999" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1999" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F130%2Fdispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="F2000" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2000" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F130%2Fdispensa-de-licitacao-n-0072022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2022</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="F2001" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2001" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F130%2Fdispensa-de-licitacao-n-0072022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2022</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr"/>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="F2002" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2002" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F85%2Fdispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="F2003" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2003" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F85%2Fdispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="F2004" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2004" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F85%2Fdispensa-de-licitacao-n-0032022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="F2005" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2005" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F85%2Fdispensa-de-licitacao-n-0032022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr"/>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="F2006" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2006" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F127%2Fdispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="F2007" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2007" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F127%2Fdispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="F2008" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2008" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F127%2Fdispensa-de-licitacao-n-0062022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2022</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="F2009" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2009" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F127%2Fdispensa-de-licitacao-n-0062022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2022</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr"/>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="F2010" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2010" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F129%2Fdispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="F2011" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2011" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F129%2Fdispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="F2012" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2012" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F129%2Fdispensa-de-licitacao-n-0042022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2022</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="F2013" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2013" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F129%2Fdispensa-de-licitacao-n-0042022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2022</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr"/>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="F2014" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2014" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F128%2Fdispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="F2015" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2015" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F128%2Fdispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="F2016" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2016" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F128%2Fdispensa-de-licitacao-n-0032022-2&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="F2017" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2017" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F128%2Fdispensa-de-licitacao-n-0032022-2&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2022</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr"/>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="F2018" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2018" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F126%2Fdispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="F2019" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2019" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F126%2Fdispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="F2020" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2020" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F126%2Fdispensa-de-licitacao-n-0022022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2022</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="F2021" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2021" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F126%2Fdispensa-de-licitacao-n-0022022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2022</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr"/>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="F2022" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2022" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2022 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F125%2Fdispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="F2023" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2023" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F125%2Fdispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="F2024" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2024" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F125%2Fdispensa-de-licitacao-n-0012022&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2022</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="F2025" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2025" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F125%2Fdispensa-de-licitacao-n-0012022&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2022</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr"/>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="F2026" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2026" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F124%2Fdispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="F2027" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2027" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F124%2Fdispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="F2028" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2028" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F124%2Fdispensa-de-licitacao-n-0122021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2021</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="F2029" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2029" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F124%2Fdispensa-de-licitacao-n-0122021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2021</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr"/>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="F2030" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2030" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F123%2Fdispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="F2031" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2031" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F123%2Fdispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="F2032" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2032" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F123%2Fdispensa-de-licitacao-n-0112021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2021</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="F2033" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2033" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F123%2Fdispensa-de-licitacao-n-0112021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2021</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr"/>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="F2034" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2034" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F122%2Fdispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="F2035" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2035" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F122%2Fdispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="F2036" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2036" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F122%2Fdispensa-de-licitacao-n-0102021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2021</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="F2037" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2037" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F122%2Fdispensa-de-licitacao-n-0102021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2021</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr"/>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="F2038" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2038" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F121%2Fdispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="F2039" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2039" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F121%2Fdispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="F2040" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2040" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F121%2Fdispensa-de-licitacao-n-0092021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2021</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="F2041" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2041" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F121%2Fdispensa-de-licitacao-n-0092021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2021</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr"/>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="F2042" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2042" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F120%2Fdispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="F2043" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2043" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F120%2Fdispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="F2044" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2044" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F120%2Fdispensa-de-licitacao-n-0082021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2021</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="F2045" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2045" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F120%2Fdispensa-de-licitacao-n-0082021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2021</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr"/>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="F2046" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2046" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F119%2Fdispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="F2047" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2047" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F119%2Fdispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="F2048" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2048" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F119%2Fdispensa-de-licitacao-n-0072021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2021</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="F2049" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2049" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F119%2Fdispensa-de-licitacao-n-0072021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2021</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr"/>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="F2050" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2050" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F118%2Fdispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="F2051" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2051" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F118%2Fdispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="F2052" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2052" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F118%2Fdispensa-de-licitacao-n-0062021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2021</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="F2053" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2053" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F118%2Fdispensa-de-licitacao-n-0062021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2021</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr"/>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="F2054" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2054" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F117%2Fdispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="F2055" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2055" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F117%2Fdispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="F2056" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2056" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F117%2Fdispensa-de-licitacao-n-0052021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2021</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="F2057" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2057" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F117%2Fdispensa-de-licitacao-n-0052021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2021</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr"/>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="F2058" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2058" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F116%2Fdispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="F2059" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2059" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F116%2Fdispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="F2060" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2060" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F116%2Fdispensa-de-licitacao-n-0042021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2021</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="F2061" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2061" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F116%2Fdispensa-de-licitacao-n-0042021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2021</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr"/>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="F2062" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2062" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F115%2Fdispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="F2063" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2063" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F115%2Fdispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="F2064" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2064" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F115%2Fdispensa-de-licitacao-n-0032021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2021</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="F2065" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2065" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F115%2Fdispensa-de-licitacao-n-0032021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2021</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr"/>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="F2066" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2066" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F114%2Fdispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="F2067" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2067" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F114%2Fdispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="F2068" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2068" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F114%2Fdispensa-de-licitacao-n-0022021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2021</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="F2069" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2069" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F114%2Fdispensa-de-licitacao-n-0022021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2021</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr"/>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="F2070" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2070" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2021 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F113%2Fdispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="F2071" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2071" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F113%2Fdispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="F2072" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2072" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F113%2Fdispensa-de-licitacao-n-0012021&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2021</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="F2073" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2073" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F113%2Fdispensa-de-licitacao-n-0012021&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2021</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr"/>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="F2074" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2074" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F112%2Fdispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="F2075" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2075" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F112%2Fdispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="F2076" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2076" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F112%2Fdispensa-de-licitacao-n-0072020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2020</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="F2077" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2077" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F112%2Fdispensa-de-licitacao-n-0072020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2020</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr"/>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="F2078" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2078" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F111%2Fdispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="F2079" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2079" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F111%2Fdispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="F2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2080" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F111%2Fdispensa-de-licitacao-n-0062020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2020</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="F2081" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2081" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F111%2Fdispensa-de-licitacao-n-0062020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2020</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr"/>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="F2082" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2082" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F84%2Fdispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="F2083" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2083" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F84%2Fdispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="F2084" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2084" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F84%2Fdispensa-de-licitacao-n-0042020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="F2085" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2085" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F84%2Fdispensa-de-licitacao-n-0042020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr"/>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="F2086" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2086" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F109%2Fdispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="F2087" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2087" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F109%2Fdispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="F2088" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2088" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F109%2Fdispensa-de-licitacao-n-0042020-2&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="F2089" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2089" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F109%2Fdispensa-de-licitacao-n-0042020-2&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2020</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr"/>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="F2090" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2090" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F83%2Fdispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="F2091" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2091" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F83%2Fdispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="F2092" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2092" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F83%2Fdispensa-de-licitacao-n-0032020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="F2093" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2093" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F83%2Fdispensa-de-licitacao-n-0032020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr"/>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="F2094" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2094" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F110%2Fdispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="F2095" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2095" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F110%2Fdispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="F2096" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2096" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F110%2Fdispensa-de-licitacao-n-0032020-2&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="F2097" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2097" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F110%2Fdispensa-de-licitacao-n-0032020-2&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2020</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr"/>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="F2098" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2098" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F107%2Fdispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="F2099" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2099" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F107%2Fdispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="F2100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2100" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F107%2Fdispensa-de-licitacao-n-0022020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2020</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="F2101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2101" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F107%2Fdispensa-de-licitacao-n-0022020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2020</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr"/>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="F2102" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2102" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2020 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F106%2Fdispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="F2103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2103" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F106%2Fdispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="F2104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2104" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F106%2Fdispensa-de-licitacao-n-0012020&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2020</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="F2105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2105" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F106%2Fdispensa-de-licitacao-n-0012020&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2020</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr"/>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="F2106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2106" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F105%2Fdispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="F2107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2107" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F105%2Fdispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="F2108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2108" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F105%2Fdispensa-de-licitacao-n-0092019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2019</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="F2109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2109" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F105%2Fdispensa-de-licitacao-n-0092019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2019</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr"/>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="F2110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2110" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F104%2Fdispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="F2111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2111" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F104%2Fdispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="F2112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2112" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F104%2Fdispensa-de-licitacao-n-0082019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2019</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="F2113" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2113" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F104%2Fdispensa-de-licitacao-n-0082019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2019</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr"/>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="F2114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2114" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F101%2Fdispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="F2115" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2115" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F101%2Fdispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="F2116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2116" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F101%2Fdispensa-de-licitacao-n-0062019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2019</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="F2117" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2117" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F101%2Fdispensa-de-licitacao-n-0062019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2019</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr"/>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="F2118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2118" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F100%2Fdispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="F2119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2119" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F100%2Fdispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="F2120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2120" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F100%2Fdispensa-de-licitacao-n-0052019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2019</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="F2121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2121" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F100%2Fdispensa-de-licitacao-n-0052019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2019</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr"/>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="F2122" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2122" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F103%2Fdispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="F2123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2123" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F103%2Fdispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="F2124" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2124" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F103%2Fdispensa-de-licitacao-n-0042019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2019</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="F2125" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2125" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F103%2Fdispensa-de-licitacao-n-0042019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2019</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr"/>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="F2126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2126" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F102%2Fdispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="F2127" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2127" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F102%2Fdispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="F2128" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2128" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F102%2Fdispensa-de-licitacao-n-0032019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2019</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="F2129" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2129" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F102%2Fdispensa-de-licitacao-n-0032019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2019</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr"/>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="F2130" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2130" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F99%2Fdispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="F2131" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2131" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F99%2Fdispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="F2132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2132" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F99%2Fdispensa-de-licitacao-n-0022019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2019</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="F2133" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2133" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F99%2Fdispensa-de-licitacao-n-0022019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2019</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr"/>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="F2134" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2134" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2019 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F98%2Fdispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="F2135" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2135" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F98%2Fdispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="F2136" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2136" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F98%2Fdispensa-de-licitacao-n-0012019&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2019</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="F2137" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2137" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F98%2Fdispensa-de-licitacao-n-0012019&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+001%2F2019</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr"/>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="F2138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2138" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F97%2Fdispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="F2139" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2139" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F97%2Fdispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="F2140" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2140" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F97%2Fdispensa-de-licitacao-n-0122018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2018</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="F2141" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2141" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F97%2Fdispensa-de-licitacao-n-0122018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+012%2F2018</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr"/>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="F2142" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2142" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F96%2Fdispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="F2143" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2143" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F96%2Fdispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="F2144" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2144" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F96%2Fdispensa-de-licitacao-n-0112018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2018</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="F2145" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2145" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F96%2Fdispensa-de-licitacao-n-0112018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+011%2F2018</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr"/>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="F2146" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2146" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F95%2Fdispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="F2147" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2147" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F95%2Fdispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="F2148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2148" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F95%2Fdispensa-de-licitacao-n-0102018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2018</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="F2149" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2149" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F95%2Fdispensa-de-licitacao-n-0102018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+010%2F2018</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr"/>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="F2150" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2150" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F94%2Fdispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="F2151" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2151" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F94%2Fdispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="F2152" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2152" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F94%2Fdispensa-de-licitacao-n-0092018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2018</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="F2153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2153" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F94%2Fdispensa-de-licitacao-n-0092018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+009%2F2018</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr"/>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="F2154" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2154" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F93%2Fdispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="F2155" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2155" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F93%2Fdispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="F2156" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2156" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F93%2Fdispensa-de-licitacao-n-0082018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2018</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="F2157" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2157" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F93%2Fdispensa-de-licitacao-n-0082018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+008%2F2018</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr"/>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="F2158" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2158" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F92%2Fdispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="F2159" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2159" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F92%2Fdispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="F2160" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2160" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F92%2Fdispensa-de-licitacao-n-0072018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2018</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="F2161" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2161" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F92%2Fdispensa-de-licitacao-n-0072018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+007%2F2018</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr"/>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="F2162" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2162" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F91%2Fdispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="F2163" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2163" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F91%2Fdispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="F2164" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2164" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F91%2Fdispensa-de-licitacao-n-0062018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2018</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="F2165" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2165" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F91%2Fdispensa-de-licitacao-n-0062018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+006%2F2018</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr"/>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="F2166" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2166" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F90%2Fdispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="F2167" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2167" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F90%2Fdispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="F2168" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2168" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F90%2Fdispensa-de-licitacao-n-0052018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2018</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="F2169" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2169" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F90%2Fdispensa-de-licitacao-n-0052018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+005%2F2018</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr"/>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="F2170" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2170" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F89%2Fdispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="F2171" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2171" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F89%2Fdispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="F2172" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2172" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F89%2Fdispensa-de-licitacao-n-0042018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2018</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="F2173" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2173" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F89%2Fdispensa-de-licitacao-n-0042018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+004%2F2018</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr"/>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="F2174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2174" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F87%2Fdispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="F2175" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2175" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F87%2Fdispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="F2176" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2176" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F87%2Fdispensa-de-licitacao-n-0032018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2018</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="F2177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2177" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F87%2Fdispensa-de-licitacao-n-0032018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+003%2F2018</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr"/>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="F2178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2178" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2018 http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F88%2Fdispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="F2179" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2179" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sharer/sharer.php?u=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F88%2Fdispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="F2180" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2180" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F88%2Fdispensa-de-licitacao-n-0022018&amp;title=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2018</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>(abre em nova guia)</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="F2181" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2181" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>https://twitter.com/intent/tweet?url=http%3A%2F%2Fwww.xambre.pr.gov.br%2Flicitacao%2Fview%2F88%2Fdispensa-de-licitacao-n-0022018&amp;text=Dispensa+de+Licita%C3%A7%C3%A3o+n%C2%B0+002%2F2018</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr"/>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="F2182" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2182" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
